--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,21</t>
+          <t>-4,03; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 14,88</t>
+          <t>7,78; 14,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,19</t>
+          <t>-2,67; 4,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,53; 19,44</t>
+          <t>12,5; 19,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,02</t>
+          <t>-2,78; 1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 17,07</t>
+          <t>11,51; 16,68</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 16,32</t>
+          <t>-37,54; 17,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73,44; 189,88</t>
+          <t>71,95; 185,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 23,3</t>
+          <t>-13,23; 24,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,22; 111,19</t>
+          <t>61,27; 111,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 14,59</t>
+          <t>-17,91; 13,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,87; 124,06</t>
+          <t>72,32; 121,55</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,25</t>
+          <t>-0,39; 1,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,6</t>
+          <t>1,84; 4,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,04</t>
+          <t>0,29; 3,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,18</t>
+          <t>2,51; 7,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,8</t>
+          <t>0,2; 1,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,48</t>
+          <t>2,93; 5,54</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 123,96</t>
+          <t>-24,35; 129,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>118,37; 488,1</t>
+          <t>120,68; 470,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 98,58</t>
+          <t>5,23; 102,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72,81; 242,82</t>
+          <t>62,79; 237,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 87,29</t>
+          <t>6,66; 87,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>113,14; 273,98</t>
+          <t>113,39; 269,32</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,49</t>
+          <t>-1,34; 2,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,62</t>
+          <t>-0,66; 2,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,4</t>
+          <t>-1,88; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 7,49</t>
+          <t>2,77; 7,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,97</t>
+          <t>-0,87; 2,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,6</t>
+          <t>1,62; 4,57</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 554,38</t>
+          <t>-64,99; 629,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 755,58</t>
+          <t>-42,87; 766,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,9; 165,32</t>
+          <t>-50,69; 192,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54,71; 566,23</t>
+          <t>52,1; 512,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,18; 169,64</t>
+          <t>-38,01; 175,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,74; 430,25</t>
+          <t>44,83; 368,57</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,34</t>
+          <t>-1,29; 0,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,21</t>
+          <t>1,52; 4,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,02</t>
+          <t>-1,77; 1,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,42</t>
+          <t>2,23; 6,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,53</t>
+          <t>-1,25; 0,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,07</t>
+          <t>2,48; 5,13</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 11,32</t>
+          <t>-31,99; 15,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,94; 129,45</t>
+          <t>42,97; 136,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 11,72</t>
+          <t>-18,04; 12,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,2; 74,16</t>
+          <t>22,89; 75,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 8,69</t>
+          <t>-18,33; 8,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,81; 83,34</t>
+          <t>38,56; 85,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,2</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,13</t>
+          <t>15,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,29</t>
+          <t>13,3</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,33</t>
+          <t>-3,96; 1,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 14,9</t>
+          <t>6,89; 14,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,33</t>
+          <t>-2,73; 3,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 19,66</t>
+          <t>12,25; 18,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,85</t>
+          <t>-2,54; 1,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,51; 16,68</t>
+          <t>10,84; 15,95</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>120,96%</t>
+          <t>109,16%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,54; 17,53</t>
+          <t>-36,88; 18,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,95; 185,36</t>
+          <t>65,05; 179,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 24,72</t>
+          <t>-13,33; 22,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61,27; 111,49</t>
+          <t>58,61; 106,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 13,17</t>
+          <t>-16,3; 13,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,32; 121,55</t>
+          <t>67,54; 117,57</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>3,91</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>6,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>5,24</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,23</t>
+          <t>-0,44; 1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,54</t>
+          <t>2,9; 5,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,05</t>
+          <t>0,28; 3,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,03</t>
+          <t>5,04; 7,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,79</t>
+          <t>0,16; 1,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,54</t>
+          <t>4,42; 6,13</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>260,59%</t>
+          <t>297,24%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147,28%</t>
+          <t>180,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>183,87%</t>
+          <t>218,35%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 129,73</t>
+          <t>-28,89; 123,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>120,68; 470,23</t>
+          <t>155,4; 536,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 102,29</t>
+          <t>5,75; 101,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62,79; 237,03</t>
+          <t>119,39; 269,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 87,03</t>
+          <t>5,9; 88,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>113,39; 269,32</t>
+          <t>158,08; 308,39</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,1</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,18</t>
+          <t>3,25</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,58</t>
+          <t>-1,08; 2,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,63</t>
+          <t>-0,92; 2,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,79</t>
+          <t>-1,68; 2,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,42</t>
+          <t>2,87; 7,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,02</t>
+          <t>-0,91; 2,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,57</t>
+          <t>1,67; 4,62</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200,01%</t>
+          <t>205,2%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>166,8%</t>
+          <t>170,79%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,99; 629,29</t>
+          <t>-63,11; 591,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 766,27</t>
+          <t>-44,34; 633,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 192,75</t>
+          <t>-49,4; 166,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,1; 512,73</t>
+          <t>61,48; 500,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 175,56</t>
+          <t>-37,32; 178,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,83; 368,57</t>
+          <t>48,76; 408,38</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,84</t>
+          <t>5,74</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>4,64</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,43</t>
+          <t>-1,25; 0,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,17</t>
+          <t>2,35; 4,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,05</t>
+          <t>-1,73; 1,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,52</t>
+          <t>4,26; 7,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,51</t>
+          <t>-1,17; 0,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,13</t>
+          <t>3,87; 5,54</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,99; 15,7</t>
+          <t>-32,1; 12,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,97; 136,5</t>
+          <t>57,17; 140,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 12,24</t>
+          <t>-17,39; 14,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,89; 75,95</t>
+          <t>42,1; 84,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 8,54</t>
+          <t>-16,58; 8,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,56; 85,06</t>
+          <t>55,28; 92,44</t>
         </is>
       </c>
     </row>
